--- a/BuildingData.xlsx
+++ b/BuildingData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>magnificationKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>priceKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,6 +67,63 @@
   </si>
   <si>
     <t>width</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_big</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_small</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>House_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>House_02</t>
+  </si>
+  <si>
+    <t>House_03</t>
+  </si>
+  <si>
+    <t>House_04</t>
+  </si>
+  <si>
+    <t>Factory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gas_Station</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Residential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stadium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>road</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Road_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Road_L_re</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Road_X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Road_T</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -401,10 +454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -412,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -438,12 +491,436 @@
       <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>2008</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>2007</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>80</v>
+      </c>
+      <c r="J3">
+        <v>80</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>2000</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>2002</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2004</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>40</v>
+      </c>
+      <c r="J6">
+        <v>40</v>
+      </c>
+      <c r="K6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>2006</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>2006</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>65</v>
+      </c>
+      <c r="J8">
+        <v>70</v>
+      </c>
+      <c r="K8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>2001</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>201</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>2002</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>300</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>2008</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>120</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>400</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>2000</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>401</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>2000</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>402</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>2000</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>403</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>2000</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>404</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>2000</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>